--- a/laporan_checkpoint_node_sample.xlsx
+++ b/laporan_checkpoint_node_sample.xlsx
@@ -4,16 +4,17 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Laporan Checkpoint" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Semua Area" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Area Showroom" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="68">
-  <si>
-    <t xml:space="preserve">  LAPORAN HASIL CHECKPOINT &amp; INSPEKSI (NODE.JS)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="51">
+  <si>
+    <t xml:space="preserve">  LAPORAN HASIL CHECKPOINT &amp; INSPEKSI (YAMAHA) - SEMUA AREA</t>
   </si>
   <si>
     <t>No. Dokumen</t>
@@ -55,9 +56,6 @@
     <t>No</t>
   </si>
   <si>
-    <t>Kode / Mandat</t>
-  </si>
-  <si>
     <t>Pertanyaan Checkpoint</t>
   </si>
   <si>
@@ -79,9 +77,6 @@
     <t xml:space="preserve">     • Sub-bagian: Garis Parkir/Arah</t>
   </si>
   <si>
-    <t>#1</t>
-  </si>
-  <si>
     <t>Apakah ada garis parkir/Arah?</t>
   </si>
   <si>
@@ -91,9 +86,6 @@
     <t>2026-07-22 18:00:52.307</t>
   </si>
   <si>
-    <t>#2</t>
-  </si>
-  <si>
     <t>Bagaimana kondisi garis parkir? Cat garis terlihat jelas, tidak ada tanaman liar, dsb</t>
   </si>
   <si>
@@ -103,15 +95,9 @@
     <t xml:space="preserve">     • Sub-bagian: Parkir Customer</t>
   </si>
   <si>
-    <t>#3</t>
-  </si>
-  <si>
     <t>Apakah ada area parkir khusus Customer?</t>
   </si>
   <si>
-    <t>#4</t>
-  </si>
-  <si>
     <t>Bagaimana kondisi parkir Customer? Rapih, ada garis parkir, ruang cukup, jumlah memadai</t>
   </si>
   <si>
@@ -121,100 +107,64 @@
     <t xml:space="preserve">     • Sub-bagian: Parkir Karyawan</t>
   </si>
   <si>
-    <t>#15</t>
-  </si>
-  <si>
     <t>Apakah ada area parkir khusus karyawan?</t>
   </si>
   <si>
-    <t>#16</t>
-  </si>
-  <si>
     <t>Bagaimana kondisi parkir karyawan? Rapih, ada garis parkir, ruang cukup, jumlah memadai</t>
   </si>
   <si>
     <t xml:space="preserve">     • Sub-bagian: Lampu area parkir</t>
   </si>
   <si>
-    <t>#10</t>
-  </si>
-  <si>
     <t>Apakah area parkir terdapat lampu?</t>
   </si>
   <si>
-    <t>#11</t>
-  </si>
-  <si>
     <t>Bagaimana kondisi lampu di area parkir? Menyala, cahaya terang, penerangan memadai</t>
   </si>
   <si>
     <t xml:space="preserve">     • Sub-bagian: Shop Sign</t>
   </si>
   <si>
-    <t>#17</t>
-  </si>
-  <si>
     <t>Apakah ada shop sign?</t>
   </si>
   <si>
-    <t>#18</t>
-  </si>
-  <si>
     <t>Bagaimana kondisi shop sign? Tulisan dan logo jelas, warna cerah (tidak kotor, pudar, dsb), Tidak terhalang, Tidak ada coretan, kotor, noda, karat, dsb dan lampu menyala</t>
   </si>
   <si>
     <t xml:space="preserve">     • Sub-bagian: Banner atau papan promosi</t>
   </si>
   <si>
-    <t>#5</t>
-  </si>
-  <si>
     <t>Apakah ada banner atau papan promosi?</t>
   </si>
   <si>
-    <t>#6</t>
-  </si>
-  <si>
     <t>Bagaimana kondisi banner atau papan promosi? Tidak rusak/robek, tidak pudar, dsb</t>
   </si>
   <si>
     <t xml:space="preserve">     • Sub-bagian: Papan Petunjuk</t>
   </si>
   <si>
-    <t>#12</t>
-  </si>
-  <si>
     <t>Apakah ada petunjuk? Masuk, Keluar, Parkir, Bengkel, dsb</t>
   </si>
   <si>
-    <t>#13</t>
-  </si>
-  <si>
     <t>Bagaimana kondisi petunjuk arah? Tidak rusak, warna tidak pudar, dsb</t>
   </si>
   <si>
     <t xml:space="preserve">     • Sub-bagian: CCTV</t>
   </si>
   <si>
-    <t>#7</t>
-  </si>
-  <si>
     <t>Apakah ada CCTV?</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>#8</t>
-  </si>
-  <si>
     <t>Apakah ada area yang tidak tersorot CCTV?</t>
   </si>
   <si>
-    <t>#9</t>
-  </si>
-  <si>
     <t>Bagaimana kondisi CCTV?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  LAPORAN HASIL CHECKPOINT &amp; INSPEKSI (YAMAHA) - AREA SHOWROOM</t>
   </si>
 </sst>
 </file>
@@ -232,7 +182,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="16"/>
+      <sz val="15"/>
       <name val="Segoe UI"/>
     </font>
     <font>
@@ -439,7 +389,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>44000</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
@@ -478,7 +428,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
@@ -517,7 +467,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
@@ -556,7 +506,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>17999</xdr:rowOff>
@@ -595,7 +545,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -634,7 +584,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -673,7 +623,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -712,7 +662,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -751,7 +701,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -790,7 +740,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -829,7 +779,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -868,7 +818,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -907,7 +857,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -946,7 +896,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -985,7 +935,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -1024,7 +974,7 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -1063,7 +1013,675 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>44000</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>17999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>17999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>17999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>17999</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>48000</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3733800" cy="971550"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>48000</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>18000</xdr:rowOff>
@@ -1425,18 +2043,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1444,51 +2061,50 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>13</v>
       </c>
@@ -1504,429 +2120,812 @@
       <c r="E7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="4" t="s">
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>19</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>2</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="11"/>
-    </row>
-    <row r="13" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>29</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>3</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>4</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="11"/>
-    </row>
-    <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>5</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>6</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="11"/>
-    </row>
-    <row r="19" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>7</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="8"/>
-    </row>
-    <row r="21" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>8</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="11"/>
-    </row>
-    <row r="22" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <v>9</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="8"/>
-    </row>
-    <row r="24" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>10</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="11"/>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="11"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <v>11</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>12</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <v>13</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="8"/>
-    </row>
-    <row r="30" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>14</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="11"/>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="11"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <v>15</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="8"/>
-    </row>
-    <row r="33" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="11">
         <v>16</v>
       </c>
-      <c r="B33" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="11"/>
-    </row>
-    <row r="34" ht="89" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="11"/>
+    </row>
+    <row r="34" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <v>17</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" s="13" t="s">
+      <c r="B34" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="8"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A7:E7"/>
+  <mergeCells count="11">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A31:E31"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>1</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>2</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>3</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="11">
+        <v>4</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>5</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="11">
+        <v>6</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
+        <v>7</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" s="8"/>
+      <c r="C20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>8</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <v>9</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="11">
+        <v>10</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="11"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
+        <v>11</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="11">
+        <v>12</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>13</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="8"/>
+    </row>
+    <row r="30" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="11">
+        <v>14</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="11"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>15</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="8"/>
+    </row>
+    <row r="33" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="11">
+        <v>16</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="11"/>
+    </row>
+    <row r="34" ht="89" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>17</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="8"/>
     </row>
   </sheetData>
+  <autoFilter ref="A7:E7"/>
   <mergeCells count="11">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A31:E31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
